--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -475,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -490,11 +478,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -505,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -520,37 +508,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -565,14 +549,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
@@ -582,14 +566,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
@@ -599,14 +583,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
@@ -616,14 +600,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
@@ -633,14 +617,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="b">
@@ -650,29 +634,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
       <c r="C13" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="b">
@@ -682,14 +668,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="b">
@@ -699,7 +685,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -716,7 +702,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -733,14 +719,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="b">
@@ -750,14 +736,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
@@ -767,31 +753,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="b">
@@ -801,14 +785,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="b">
@@ -818,14 +802,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="b">
@@ -835,14 +819,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="C24" t="n">
-        <v>-1</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="b">
@@ -852,14 +836,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="b">
@@ -869,14 +853,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="b">
@@ -886,31 +870,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="b">
@@ -920,14 +902,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="b">
@@ -937,14 +919,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="b">
@@ -954,14 +936,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D31" t="n">
         <v>-0.4333333333333333</v>
@@ -973,14 +955,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>-0.4333333333333333</v>
@@ -992,17 +974,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
@@ -1011,36 +993,34 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
@@ -1049,17 +1029,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
@@ -1068,17 +1048,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -1087,34 +1067,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
       <c r="C38" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D38" t="n">
         <v>-0.3</v>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
@@ -1123,32 +1105,34 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
       <c r="C40" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -1157,17 +1141,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
@@ -1176,17 +1160,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
@@ -1195,15 +1179,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -1212,17 +1196,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
@@ -1231,34 +1215,36 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>-2</v>
+      </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
@@ -1267,36 +1253,34 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
@@ -1305,17 +1289,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
@@ -1324,17 +1308,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
@@ -1343,24 +1327,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1370,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
@@ -1379,7 +1365,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1389,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
@@ -1398,26 +1384,24 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1427,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
@@ -1436,7 +1420,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1446,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
@@ -1455,7 +1439,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1465,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
@@ -1474,7 +1458,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1484,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
@@ -1493,17 +1477,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D60" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
@@ -1512,74 +1496,68 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
@@ -1588,36 +1566,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D66" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E66" t="b">
         <v>1</v>
@@ -1626,32 +1602,34 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
         <v>-0.8571428571428571</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.3</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -1660,51 +1638,55 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
       <c r="C69" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
       <c r="C70" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
@@ -1713,17 +1695,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>-2.428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E72" t="b">
         <v>1</v>
@@ -1732,17 +1714,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>-2.285714285714286</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E73" t="b">
         <v>1</v>
@@ -1751,17 +1733,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
@@ -1770,17 +1752,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.428571428571429</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E75" t="b">
         <v>1</v>
@@ -1789,36 +1771,34 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>-3</v>
-      </c>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-1.428571428571429</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E77" t="b">
         <v>1</v>
@@ -1827,17 +1807,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
@@ -1846,17 +1826,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
@@ -1865,17 +1845,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E80" t="b">
         <v>1</v>
@@ -1884,17 +1864,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
@@ -1903,17 +1883,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
@@ -1922,7 +1902,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1932,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E83" t="b">
         <v>1</v>
@@ -1941,7 +1921,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1951,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E84" t="b">
         <v>1</v>
@@ -1960,17 +1940,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E85" t="b">
         <v>1</v>
@@ -1979,17 +1959,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E86" t="b">
         <v>1</v>
@@ -1998,17 +1978,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E87" t="b">
         <v>1</v>
@@ -2017,17 +1997,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E88" t="b">
         <v>1</v>
@@ -2036,17 +2016,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E89" t="b">
         <v>1</v>
@@ -2055,36 +2035,34 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E91" t="b">
         <v>1</v>
@@ -2093,7 +2071,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2103,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E92" t="b">
         <v>1</v>
@@ -2112,7 +2090,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2122,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E93" t="b">
         <v>1</v>
@@ -2131,7 +2109,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2141,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E94" t="b">
         <v>1</v>
@@ -2150,7 +2128,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2160,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E95" t="b">
         <v>1</v>
@@ -2169,7 +2147,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2179,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E96" t="b">
         <v>1</v>
@@ -2188,7 +2166,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2198,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E97" t="b">
         <v>1</v>
@@ -2207,24 +2185,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2234,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E99" t="b">
         <v>1</v>
@@ -2243,7 +2223,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2253,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E100" t="b">
         <v>1</v>
@@ -2262,7 +2242,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2272,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E101" t="b">
         <v>1</v>
@@ -2281,70 +2261,72 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>-3</v>
+      </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E105" t="b">
         <v>1</v>
@@ -2353,34 +2335,36 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E107" t="b">
         <v>1</v>
@@ -2389,17 +2373,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E108" t="b">
         <v>1</v>
@@ -2408,17 +2392,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E109" t="b">
         <v>1</v>
@@ -2427,17 +2411,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>-2</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E110" t="b">
         <v>1</v>
@@ -2446,85 +2430,93 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
       <c r="C111" t="n">
         <v>-0.5714285714285714</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
       <c r="C112" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
       <c r="C113" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>-2</v>
+      </c>
       <c r="C114" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="C115" t="n">
-        <v>-1.714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E115" t="b">
         <v>1</v>
@@ -2533,17 +2525,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>-2</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E116" t="b">
         <v>1</v>
@@ -2552,17 +2544,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E117" t="b">
         <v>1</v>
@@ -2571,17 +2563,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E118" t="b">
         <v>1</v>
@@ -2590,17 +2582,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E119" t="b">
         <v>1</v>
@@ -2609,17 +2601,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E120" t="b">
         <v>1</v>
@@ -2628,34 +2620,36 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
       <c r="C121" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E122" t="b">
         <v>1</v>
@@ -2664,17 +2658,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E123" t="b">
         <v>1</v>
@@ -2683,34 +2677,1725 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
       <c r="C124" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.6</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-0.3666666666666666</v>
+      </c>
+      <c r="E128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E134" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E139" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E140" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E141" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E145" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E147" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E148" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E149" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E151" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E152" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E153" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E154" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E155" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E156" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E157" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D160" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D161" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E161" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E162" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D163" t="n">
+        <v>-0.5666666666666667</v>
+      </c>
+      <c r="E163" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="D164" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-1.857142857142857</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E165" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D166" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E166" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D167" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E167" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E169" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.7142857142857143</v>
+      </c>
+      <c r="D170" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E173" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E174" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E176" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E177" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E179" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E180" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E181" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E182" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E183" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E185" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>0</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E186" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E187" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E188" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E189" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E190" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E191" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E192" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="E193" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E194" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E195" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E196" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>0</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D201" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E201" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D202" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E202" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D203" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E203" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D204" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="E204" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D205" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E205" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C206" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D206" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E206" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C207" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D207" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E207" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
+      <c r="C208" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D208" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E208" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0</v>
+      </c>
+      <c r="C209" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D209" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E209" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>0</v>
+      </c>
+      <c r="C210" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D210" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E210" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>0</v>
+      </c>
+      <c r="C211" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D211" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E211" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D212" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E212" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0</v>
+      </c>
+      <c r="C213" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D213" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E213" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C214" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D214" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E214" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D215" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E215" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="n">
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="n">
         <v>-0.8571428571428571</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D216" t="n">
         <v>-0.6666666666666666</v>
       </c>
-      <c r="E125" t="b">
+      <c r="E216" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2735,21 +4420,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>India WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2025-11-19 to 2026-03-22 | Publication days: 102</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2025-08-20 to 2026-03-22 | Publication days: 177</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -2757,22 +4442,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E216"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -463,11 +463,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -478,11 +478,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -508,33 +508,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -549,14 +553,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
@@ -566,14 +570,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
@@ -583,14 +587,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
@@ -600,14 +604,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
@@ -617,14 +621,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="b">
@@ -634,14 +638,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="b">
@@ -651,14 +655,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="b">
@@ -668,14 +672,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="b">
@@ -685,14 +689,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="b">
@@ -702,14 +706,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="b">
@@ -719,14 +723,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="b">
@@ -736,14 +740,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
@@ -753,63 +757,61 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
       <c r="C20" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="b">
@@ -819,14 +821,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="b">
@@ -836,14 +838,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>-2</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="b">
@@ -853,14 +855,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="b">
@@ -870,29 +872,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-2</v>
+      </c>
       <c r="C27" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="b">
@@ -902,14 +906,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="b">
@@ -919,14 +923,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="b">
@@ -936,17 +940,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
@@ -955,17 +959,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -974,53 +978,53 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D33" t="n">
         <v>-0.3666666666666666</v>
       </c>
       <c r="E33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
@@ -1029,17 +1033,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
@@ -1048,17 +1052,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -1067,17 +1071,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -1086,17 +1090,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
@@ -1105,53 +1109,53 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
       <c r="C41" t="n">
-        <v>0.2857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2857142857142857</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
@@ -1160,17 +1164,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>-2</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
@@ -1179,34 +1183,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>-3</v>
+      </c>
       <c r="C44" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
@@ -1215,17 +1221,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>-2</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -1234,17 +1240,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
@@ -1253,34 +1259,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
       <c r="C48" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
@@ -1289,17 +1297,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
@@ -1308,17 +1316,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
@@ -1327,17 +1335,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.9</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
@@ -1346,17 +1354,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
@@ -1365,17 +1373,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
@@ -1384,34 +1392,36 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.8</v>
       </c>
       <c r="E56" t="b">
         <v>1</v>
@@ -1420,17 +1430,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
@@ -1439,17 +1449,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
@@ -1458,17 +1468,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
@@ -1477,17 +1487,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.2</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
@@ -1496,15 +1506,15 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -1513,32 +1523,34 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
       <c r="C62" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.4</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -1547,17 +1559,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.4</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
@@ -1566,34 +1578,36 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
       <c r="C65" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.4</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="E66" t="b">
         <v>1</v>
@@ -1602,17 +1616,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E67" t="b">
         <v>1</v>
@@ -1621,53 +1635,53 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E70" t="b">
         <v>1</v>
@@ -1676,17 +1690,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
@@ -1695,17 +1709,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.4</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E72" t="b">
         <v>1</v>
@@ -1714,17 +1728,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C73" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E73" t="b">
         <v>1</v>
@@ -1733,17 +1747,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
@@ -1752,17 +1766,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E75" t="b">
         <v>1</v>
@@ -1771,34 +1785,36 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
       <c r="C76" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E77" t="b">
         <v>1</v>
@@ -1807,17 +1823,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
@@ -1826,17 +1842,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
@@ -1845,17 +1861,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E80" t="b">
         <v>1</v>
@@ -1864,17 +1880,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
@@ -1883,17 +1899,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
@@ -1902,36 +1918,34 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.2</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E84" t="b">
         <v>1</v>
@@ -1940,17 +1954,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E85" t="b">
         <v>1</v>
@@ -1959,17 +1973,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E86" t="b">
         <v>1</v>
@@ -1978,17 +1992,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E87" t="b">
         <v>1</v>
@@ -1997,36 +2011,34 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E89" t="b">
         <v>1</v>
@@ -2035,31 +2047,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
         <v>-0.4285714285714285</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
         <v>-0.1666666666666667</v>
@@ -2071,7 +2085,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2081,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.1</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E92" t="b">
         <v>1</v>
@@ -2090,7 +2104,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2100,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E93" t="b">
         <v>1</v>
@@ -2109,17 +2123,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E94" t="b">
         <v>1</v>
@@ -2128,17 +2142,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E95" t="b">
         <v>1</v>
@@ -2147,55 +2161,51 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E98" t="b">
         <v>1</v>
@@ -2204,17 +2214,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E99" t="b">
         <v>1</v>
@@ -2223,17 +2233,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.1</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E100" t="b">
         <v>1</v>
@@ -2242,17 +2252,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.1</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E101" t="b">
         <v>1</v>
@@ -2261,17 +2271,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E102" t="b">
         <v>1</v>
@@ -2280,17 +2290,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.2</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E103" t="b">
         <v>1</v>
@@ -2299,31 +2309,33 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
       <c r="C104" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D105" t="n">
         <v>-0.2</v>
@@ -2335,14 +2347,14 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D106" t="n">
         <v>-0.2</v>
@@ -2354,7 +2366,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2373,7 +2385,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2392,17 +2404,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E109" t="b">
         <v>1</v>
@@ -2411,17 +2423,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E110" t="b">
         <v>1</v>
@@ -2430,36 +2442,34 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B112" t="n">
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E112" t="b">
         <v>1</v>
@@ -2468,17 +2478,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E113" t="b">
         <v>1</v>
@@ -2487,17 +2497,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E114" t="b">
         <v>1</v>
@@ -2506,17 +2516,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="C115" t="n">
-        <v>-1</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E115" t="b">
         <v>1</v>
@@ -2525,17 +2535,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E116" t="b">
         <v>1</v>
@@ -2544,17 +2554,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E117" t="b">
         <v>1</v>
@@ -2563,36 +2573,34 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E119" t="b">
         <v>1</v>
@@ -2601,17 +2609,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E120" t="b">
         <v>1</v>
@@ -2620,17 +2628,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E121" t="b">
         <v>1</v>
@@ -2639,14 +2647,14 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D122" t="n">
         <v>-0.4333333333333333</v>
@@ -2658,14 +2666,14 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
         <v>-0.4333333333333333</v>
@@ -2677,17 +2685,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E124" t="b">
         <v>1</v>
@@ -2696,36 +2704,34 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E126" t="b">
         <v>1</v>
@@ -2734,17 +2740,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E127" t="b">
         <v>1</v>
@@ -2753,17 +2759,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>2</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E128" t="b">
         <v>1</v>
@@ -2772,34 +2778,36 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
       <c r="C129" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D129" t="n">
         <v>-0.3</v>
       </c>
       <c r="E129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E130" t="b">
         <v>1</v>
@@ -2808,32 +2816,34 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
       <c r="C131" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E132" t="b">
         <v>0</v>
@@ -2842,17 +2852,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E133" t="b">
         <v>1</v>
@@ -2861,17 +2871,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C134" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E134" t="b">
         <v>1</v>
@@ -2880,15 +2890,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E135" t="b">
         <v>0</v>
@@ -2897,17 +2907,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E136" t="b">
         <v>1</v>
@@ -2916,34 +2926,36 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>-2</v>
+      </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E138" t="b">
         <v>1</v>
@@ -2952,36 +2964,34 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E140" t="b">
         <v>1</v>
@@ -2990,17 +3000,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B141" t="n">
         <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E141" t="b">
         <v>1</v>
@@ -3009,17 +3019,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E142" t="b">
         <v>1</v>
@@ -3028,24 +3038,26 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3055,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E144" t="b">
         <v>1</v>
@@ -3064,7 +3076,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3074,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E145" t="b">
         <v>1</v>
@@ -3083,26 +3095,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3112,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E147" t="b">
         <v>1</v>
@@ -3121,7 +3131,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3131,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E148" t="b">
         <v>1</v>
@@ -3140,7 +3150,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3150,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E149" t="b">
         <v>1</v>
@@ -3159,7 +3169,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3169,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E150" t="b">
         <v>1</v>
@@ -3178,17 +3188,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D151" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E151" t="b">
         <v>1</v>
@@ -3197,74 +3207,68 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D152" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D153" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D154" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D155" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E155" t="b">
         <v>1</v>
@@ -3273,36 +3277,34 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D156" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D157" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E157" t="b">
         <v>1</v>
@@ -3311,32 +3313,34 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
       <c r="C158" t="n">
         <v>-0.8571428571428571</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.3</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E159" t="b">
         <v>0</v>
@@ -3345,51 +3349,55 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0</v>
+      </c>
       <c r="C160" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>2</v>
+      </c>
       <c r="C161" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E162" t="b">
         <v>1</v>
@@ -3398,17 +3406,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>-2.428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E163" t="b">
         <v>1</v>
@@ -3417,17 +3425,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>-2.285714285714286</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E164" t="b">
         <v>1</v>
@@ -3436,17 +3444,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>-1.857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E165" t="b">
         <v>1</v>
@@ -3455,17 +3463,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>-1.428571428571429</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E166" t="b">
         <v>1</v>
@@ -3474,36 +3482,34 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>-3</v>
-      </c>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>-1.428571428571429</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E168" t="b">
         <v>1</v>
@@ -3512,17 +3518,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E169" t="b">
         <v>1</v>
@@ -3531,17 +3537,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E170" t="b">
         <v>1</v>
@@ -3550,17 +3556,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E171" t="b">
         <v>1</v>
@@ -3569,17 +3575,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B172" t="n">
         <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E172" t="b">
         <v>1</v>
@@ -3588,17 +3594,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E173" t="b">
         <v>1</v>
@@ -3607,7 +3613,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3617,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E174" t="b">
         <v>1</v>
@@ -3626,7 +3632,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3636,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E175" t="b">
         <v>1</v>
@@ -3645,17 +3651,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E176" t="b">
         <v>1</v>
@@ -3664,17 +3670,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E177" t="b">
         <v>1</v>
@@ -3683,17 +3689,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E178" t="b">
         <v>1</v>
@@ -3702,17 +3708,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E179" t="b">
         <v>1</v>
@@ -3721,17 +3727,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E180" t="b">
         <v>1</v>
@@ -3740,36 +3746,34 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E182" t="b">
         <v>1</v>
@@ -3778,7 +3782,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3788,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E183" t="b">
         <v>1</v>
@@ -3797,7 +3801,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3807,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E184" t="b">
         <v>1</v>
@@ -3816,7 +3820,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -3826,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E185" t="b">
         <v>1</v>
@@ -3835,7 +3839,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3845,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E186" t="b">
         <v>1</v>
@@ -3854,7 +3858,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3864,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E187" t="b">
         <v>1</v>
@@ -3873,7 +3877,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -3883,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E188" t="b">
         <v>1</v>
@@ -3892,24 +3896,26 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr"/>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3919,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E190" t="b">
         <v>1</v>
@@ -3928,7 +3934,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3938,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E191" t="b">
         <v>1</v>
@@ -3947,7 +3953,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3957,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E192" t="b">
         <v>1</v>
@@ -3966,70 +3972,72 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr"/>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>-3</v>
+      </c>
       <c r="C193" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr"/>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>0</v>
+      </c>
       <c r="C194" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B196" t="n">
         <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E196" t="b">
         <v>1</v>
@@ -4038,34 +4046,36 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr"/>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E198" t="b">
         <v>1</v>
@@ -4074,17 +4084,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E199" t="b">
         <v>1</v>
@@ -4093,17 +4103,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E200" t="b">
         <v>1</v>
@@ -4112,17 +4122,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>-2</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E201" t="b">
         <v>1</v>
@@ -4131,85 +4141,93 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
       <c r="C202" t="n">
         <v>-0.5714285714285714</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>0</v>
+      </c>
       <c r="C203" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr"/>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
       <c r="C204" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr"/>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>-2</v>
+      </c>
       <c r="C205" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="C206" t="n">
-        <v>-1.714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E206" t="b">
         <v>1</v>
@@ -4218,17 +4236,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>-2</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E207" t="b">
         <v>1</v>
@@ -4237,17 +4255,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="B208" t="n">
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E208" t="b">
         <v>1</v>
@@ -4256,17 +4274,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="B209" t="n">
         <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E209" t="b">
         <v>1</v>
@@ -4275,17 +4293,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B210" t="n">
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E210" t="b">
         <v>1</v>
@@ -4294,17 +4312,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D211" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E211" t="b">
         <v>1</v>
@@ -4313,34 +4331,36 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr"/>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>0</v>
+      </c>
       <c r="C212" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E213" t="b">
         <v>1</v>
@@ -4349,17 +4369,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E214" t="b">
         <v>1</v>
@@ -4368,34 +4388,1725 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr"/>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>0</v>
+      </c>
       <c r="C215" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.6</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>0</v>
+      </c>
+      <c r="C216" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D216" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E216" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>0</v>
+      </c>
+      <c r="C217" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D217" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E217" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0</v>
+      </c>
+      <c r="C218" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D218" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E218" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2</v>
+      </c>
+      <c r="C219" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="D219" t="n">
+        <v>-0.3666666666666666</v>
+      </c>
+      <c r="E219" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D220" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E220" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>0</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D221" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E221" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D222" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E222" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D223" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E223" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D224" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E224" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>0</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E225" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D226" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E226" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>0</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E227" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E228" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>0</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E229" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E230" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>0</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E231" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E232" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E233" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E234" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E236" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E237" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E238" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E239" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E240" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E241" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E242" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E243" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E244" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E245" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E246" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E247" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C248" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E248" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D249" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E249" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="D250" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E250" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D251" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E251" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D252" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E252" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0</v>
+      </c>
+      <c r="C253" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D253" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E253" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C254" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D254" t="n">
+        <v>-0.5666666666666667</v>
+      </c>
+      <c r="E254" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C255" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="D255" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E255" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>0</v>
+      </c>
+      <c r="C256" t="n">
+        <v>-1.857142857142857</v>
+      </c>
+      <c r="D256" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E256" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>0</v>
+      </c>
+      <c r="C257" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D257" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E257" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C258" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D258" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E258" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>0</v>
+      </c>
+      <c r="C259" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D259" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E259" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0</v>
+      </c>
+      <c r="C260" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D260" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E260" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
+      <c r="C261" t="n">
+        <v>-0.7142857142857143</v>
+      </c>
+      <c r="D261" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E261" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0</v>
+      </c>
+      <c r="C262" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D262" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E262" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0</v>
+      </c>
+      <c r="C263" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D263" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E263" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0</v>
+      </c>
+      <c r="C264" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D264" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E264" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>0</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0</v>
+      </c>
+      <c r="D265" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E265" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E266" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E267" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E268" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E269" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E270" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E271" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E272" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>0</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E273" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E274" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E275" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E276" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>0</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E277" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>0</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E278" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E279" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E280" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E281" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E282" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0</v>
+      </c>
+      <c r="D283" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E283" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="n">
+        <v>0</v>
+      </c>
+      <c r="D284" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="E284" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E285" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0</v>
+      </c>
+      <c r="D286" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E286" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E287" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="n">
+        <v>0</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C292" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D292" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E292" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D293" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E293" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D294" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E294" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D295" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="E295" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D296" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E296" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C297" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D297" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E297" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C298" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D298" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E298" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0</v>
+      </c>
+      <c r="C299" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D299" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E299" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0</v>
+      </c>
+      <c r="C300" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D300" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E300" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>0</v>
+      </c>
+      <c r="C301" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D301" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E301" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0</v>
+      </c>
+      <c r="C302" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D302" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E302" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+      <c r="C303" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D303" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E303" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0</v>
+      </c>
+      <c r="C304" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D304" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E304" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C305" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D305" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E305" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+      <c r="C306" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D306" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E306" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
-      <c r="C216" t="n">
+      <c r="B307" t="inlineStr"/>
+      <c r="C307" t="n">
         <v>-0.8571428571428571</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D307" t="n">
         <v>-0.6666666666666666</v>
       </c>
-      <c r="E216" t="b">
+      <c r="E307" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4429,7 +6140,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-08-20 to 2026-03-22 | Publication days: 177</t>
+          <t>Coverage: 2025-05-21 to 2026-03-22 | Publication days: 259</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -463,11 +463,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -478,11 +478,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -523,11 +523,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -553,14 +553,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
@@ -570,14 +570,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
@@ -587,14 +587,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
@@ -604,14 +604,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
@@ -621,14 +621,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="b">
@@ -638,24 +638,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -672,7 +670,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -689,7 +687,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -706,7 +704,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -723,7 +721,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -740,14 +738,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
@@ -757,14 +755,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="b">
@@ -774,44 +772,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
       <c r="C22" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="b">
@@ -821,14 +823,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="b">
@@ -838,14 +840,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>-2</v>
       </c>
       <c r="C25" t="n">
-        <v>-1</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="b">
@@ -855,14 +857,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="b">
@@ -872,14 +874,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-1</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="b">
@@ -889,14 +891,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C28" t="n">
-        <v>-1</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="b">
@@ -906,11 +908,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C29" t="n">
         <v>-1</v>
@@ -923,14 +925,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="b">
@@ -940,17 +942,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
@@ -959,17 +961,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -978,72 +980,70 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
       <c r="C33" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.2</v>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2</v>
-      </c>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>-3</v>
-      </c>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
@@ -1052,17 +1052,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -1071,17 +1071,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -1090,17 +1090,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
@@ -1109,72 +1109,70 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
       <c r="C40" t="n">
-        <v>-1</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.6</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.6</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
@@ -1183,17 +1181,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
@@ -1202,17 +1200,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
@@ -1221,17 +1219,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>-2</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -1240,17 +1238,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C47" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.9</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
@@ -1259,17 +1257,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.9</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
@@ -1278,17 +1276,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>-1</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
@@ -1297,17 +1295,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>-1</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.9</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
@@ -1316,17 +1314,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.9</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
@@ -1335,7 +1333,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1345,7 +1343,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
@@ -1354,7 +1352,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1364,7 +1362,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.8</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
@@ -1373,17 +1371,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.8</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
@@ -1392,55 +1390,51 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="E56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
@@ -1449,17 +1443,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
@@ -1468,17 +1462,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
@@ -1487,17 +1481,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C60" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
@@ -1506,24 +1500,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
       <c r="C61" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1533,7 +1529,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
@@ -1542,34 +1538,36 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E64" t="b">
         <v>1</v>
@@ -1578,17 +1576,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E65" t="b">
         <v>1</v>
@@ -1597,17 +1595,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E66" t="b">
         <v>1</v>
@@ -1616,36 +1614,34 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E68" t="b">
         <v>1</v>
@@ -1654,15 +1650,15 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.6</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E69" t="b">
         <v>0</v>
@@ -1671,36 +1667,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E71" t="b">
         <v>1</v>
@@ -1709,17 +1703,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E72" t="b">
         <v>1</v>
@@ -1728,17 +1722,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E73" t="b">
         <v>1</v>
@@ -1747,17 +1741,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.4</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
@@ -1766,17 +1760,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C75" t="n">
         <v>-0.5714285714285714</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.4</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E75" t="b">
         <v>1</v>
@@ -1785,17 +1779,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E76" t="b">
         <v>1</v>
@@ -1804,36 +1798,34 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
@@ -1842,17 +1834,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
@@ -1861,17 +1853,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-2</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.9</v>
       </c>
       <c r="E80" t="b">
         <v>1</v>
@@ -1880,17 +1872,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-2.428571428571428</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
@@ -1899,17 +1891,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1428571428571428</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-1.1</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
@@ -1918,15 +1910,15 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0.5714285714285714</v>
+        <v>-2.714285714285714</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-1.2</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
@@ -1935,36 +1927,34 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>-3</v>
-      </c>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>0.1428571428571428</v>
+        <v>-2.857142857142857</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-1.3</v>
       </c>
       <c r="E84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1428571428571428</v>
+        <v>-2.714285714285714</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E85" t="b">
         <v>1</v>
@@ -1973,17 +1963,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1428571428571428</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E86" t="b">
         <v>1</v>
@@ -1992,17 +1982,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1428571428571428</v>
+        <v>-2</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E87" t="b">
         <v>1</v>
@@ -2011,15 +2001,15 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0.4285714285714285</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
@@ -2028,36 +2018,34 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.3</v>
       </c>
       <c r="E90" t="b">
         <v>1</v>
@@ -2066,17 +2054,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.3</v>
       </c>
       <c r="E91" t="b">
         <v>1</v>
@@ -2085,7 +2073,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2095,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.3</v>
       </c>
       <c r="E92" t="b">
         <v>1</v>
@@ -2104,17 +2092,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.466666666666667</v>
       </c>
       <c r="E93" t="b">
         <v>1</v>
@@ -2123,17 +2111,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="E94" t="b">
         <v>1</v>
@@ -2142,17 +2130,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>0</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-1.4</v>
       </c>
       <c r="E95" t="b">
         <v>1</v>
@@ -2161,51 +2149,55 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.3</v>
       </c>
       <c r="E96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
       <c r="C97" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.2</v>
       </c>
       <c r="E97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.2</v>
       </c>
       <c r="E98" t="b">
         <v>1</v>
@@ -2214,17 +2206,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.2</v>
       </c>
       <c r="E99" t="b">
         <v>1</v>
@@ -2233,17 +2225,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-1.2</v>
       </c>
       <c r="E100" t="b">
         <v>1</v>
@@ -2252,17 +2244,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-1.2</v>
       </c>
       <c r="E101" t="b">
         <v>1</v>
@@ -2271,17 +2263,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-1.133333333333333</v>
       </c>
       <c r="E102" t="b">
         <v>1</v>
@@ -2290,17 +2282,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-1.133333333333333</v>
       </c>
       <c r="E103" t="b">
         <v>1</v>
@@ -2309,17 +2301,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.1</v>
+        <v>-1.133333333333333</v>
       </c>
       <c r="E104" t="b">
         <v>1</v>
@@ -2328,17 +2320,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.2</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="E105" t="b">
         <v>1</v>
@@ -2347,17 +2339,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="E106" t="b">
         <v>1</v>
@@ -2366,17 +2358,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.2</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E107" t="b">
         <v>1</v>
@@ -2385,17 +2377,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.2</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E108" t="b">
         <v>1</v>
@@ -2404,17 +2396,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.2</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E109" t="b">
         <v>1</v>
@@ -2423,17 +2415,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.2</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E110" t="b">
         <v>1</v>
@@ -2442,72 +2434,70 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
       <c r="C111" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.4</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.3</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E114" t="b">
         <v>1</v>
@@ -2516,14 +2506,14 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D115" t="n">
         <v>-0.3666666666666666</v>
@@ -2535,14 +2525,14 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>-2</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D116" t="n">
         <v>-0.4333333333333333</v>
@@ -2554,14 +2544,14 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D117" t="n">
         <v>-0.4333333333333333</v>
@@ -2573,34 +2563,36 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>-2</v>
+      </c>
       <c r="C118" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B119" t="n">
         <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E119" t="b">
         <v>1</v>
@@ -2609,17 +2601,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E120" t="b">
         <v>1</v>
@@ -2628,17 +2620,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E121" t="b">
         <v>1</v>
@@ -2647,17 +2639,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E122" t="b">
         <v>1</v>
@@ -2666,17 +2658,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E123" t="b">
         <v>1</v>
@@ -2685,53 +2677,53 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D124" t="n">
         <v>-0.3666666666666666</v>
       </c>
       <c r="E124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2</v>
+      </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E126" t="b">
         <v>1</v>
@@ -2740,17 +2732,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.4</v>
       </c>
       <c r="E127" t="b">
         <v>1</v>
@@ -2759,17 +2751,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E128" t="b">
         <v>1</v>
@@ -2778,17 +2770,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E129" t="b">
         <v>1</v>
@@ -2797,17 +2789,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E130" t="b">
         <v>1</v>
@@ -2816,53 +2808,53 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
       <c r="C132" t="n">
-        <v>0.2857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.6</v>
       </c>
       <c r="E132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2857142857142857</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E133" t="b">
         <v>1</v>
@@ -2871,17 +2863,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>-2</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.3</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E134" t="b">
         <v>1</v>
@@ -2890,34 +2882,36 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>-3</v>
+      </c>
       <c r="C135" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E136" t="b">
         <v>1</v>
@@ -2926,17 +2920,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B137" t="n">
         <v>-2</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E137" t="b">
         <v>1</v>
@@ -2945,17 +2939,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E138" t="b">
         <v>1</v>
@@ -2964,34 +2958,36 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
       <c r="C139" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B140" t="n">
         <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E140" t="b">
         <v>1</v>
@@ -3000,17 +2996,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E141" t="b">
         <v>1</v>
@@ -3019,17 +3015,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E142" t="b">
         <v>1</v>
@@ -3038,17 +3034,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.9</v>
       </c>
       <c r="E143" t="b">
         <v>1</v>
@@ -3057,17 +3053,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="B144" t="n">
         <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E144" t="b">
         <v>1</v>
@@ -3076,17 +3072,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="E145" t="b">
         <v>1</v>
@@ -3095,34 +3091,36 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.8</v>
       </c>
       <c r="E147" t="b">
         <v>1</v>
@@ -3131,17 +3129,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B148" t="n">
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E148" t="b">
         <v>1</v>
@@ -3150,17 +3148,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E149" t="b">
         <v>1</v>
@@ -3169,17 +3167,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B150" t="n">
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E150" t="b">
         <v>1</v>
@@ -3188,17 +3186,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.2</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E151" t="b">
         <v>1</v>
@@ -3207,15 +3205,15 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E152" t="b">
         <v>0</v>
@@ -3224,32 +3222,34 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0</v>
+      </c>
       <c r="C153" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.4</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
@@ -3258,17 +3258,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.4</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E155" t="b">
         <v>1</v>
@@ -3277,34 +3277,36 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
       <c r="C156" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.4</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C157" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="E157" t="b">
         <v>1</v>
@@ -3313,17 +3315,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E158" t="b">
         <v>1</v>
@@ -3332,53 +3334,53 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
       <c r="C159" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E161" t="b">
         <v>1</v>
@@ -3387,17 +3389,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="E162" t="b">
         <v>1</v>
@@ -3406,17 +3408,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B163" t="n">
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.4</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E163" t="b">
         <v>1</v>
@@ -3425,17 +3427,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C164" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E164" t="b">
         <v>1</v>
@@ -3444,17 +3446,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C165" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E165" t="b">
         <v>1</v>
@@ -3463,17 +3465,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E166" t="b">
         <v>1</v>
@@ -3482,34 +3484,36 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
       <c r="C167" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E168" t="b">
         <v>1</v>
@@ -3518,17 +3522,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E169" t="b">
         <v>1</v>
@@ -3537,17 +3541,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E170" t="b">
         <v>1</v>
@@ -3556,17 +3560,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E171" t="b">
         <v>1</v>
@@ -3575,17 +3579,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E172" t="b">
         <v>1</v>
@@ -3594,17 +3598,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E173" t="b">
         <v>1</v>
@@ -3613,36 +3617,34 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.2</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E175" t="b">
         <v>1</v>
@@ -3651,17 +3653,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E176" t="b">
         <v>1</v>
@@ -3670,17 +3672,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E177" t="b">
         <v>1</v>
@@ -3689,17 +3691,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E178" t="b">
         <v>1</v>
@@ -3708,36 +3710,34 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E180" t="b">
         <v>1</v>
@@ -3746,31 +3746,33 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr"/>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
       <c r="C181" t="n">
         <v>-0.4285714285714285</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
         <v>-0.1666666666666667</v>
@@ -3782,7 +3784,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3792,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.1</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E183" t="b">
         <v>1</v>
@@ -3801,7 +3803,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3811,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E184" t="b">
         <v>1</v>
@@ -3820,17 +3822,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E185" t="b">
         <v>1</v>
@@ -3839,17 +3841,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E186" t="b">
         <v>1</v>
@@ -3858,55 +3860,51 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E189" t="b">
         <v>1</v>
@@ -3915,17 +3913,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B190" t="n">
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E190" t="b">
         <v>1</v>
@@ -3934,17 +3932,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.1</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E191" t="b">
         <v>1</v>
@@ -3953,17 +3951,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B192" t="n">
         <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.1</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E192" t="b">
         <v>1</v>
@@ -3972,17 +3970,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E193" t="b">
         <v>1</v>
@@ -3991,17 +3989,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B194" t="n">
         <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.2</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E194" t="b">
         <v>1</v>
@@ -4010,31 +4008,33 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr"/>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
       <c r="C195" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D196" t="n">
         <v>-0.2</v>
@@ -4046,14 +4046,14 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D197" t="n">
         <v>-0.2</v>
@@ -4065,7 +4065,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4084,7 +4084,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4103,17 +4103,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E200" t="b">
         <v>1</v>
@@ -4122,17 +4122,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E201" t="b">
         <v>1</v>
@@ -4141,36 +4141,34 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B203" t="n">
         <v>0</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E203" t="b">
         <v>1</v>
@@ -4179,17 +4177,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E204" t="b">
         <v>1</v>
@@ -4198,17 +4196,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E205" t="b">
         <v>1</v>
@@ -4217,17 +4215,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="C206" t="n">
-        <v>-1</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E206" t="b">
         <v>1</v>
@@ -4236,17 +4234,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E207" t="b">
         <v>1</v>
@@ -4255,17 +4253,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B208" t="n">
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E208" t="b">
         <v>1</v>
@@ -4274,36 +4272,34 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B210" t="n">
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E210" t="b">
         <v>1</v>
@@ -4312,17 +4308,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D211" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E211" t="b">
         <v>1</v>
@@ -4331,17 +4327,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B212" t="n">
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E212" t="b">
         <v>1</v>
@@ -4350,14 +4346,14 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D213" t="n">
         <v>-0.4333333333333333</v>
@@ -4369,14 +4365,14 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B214" t="n">
         <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D214" t="n">
         <v>-0.4333333333333333</v>
@@ -4388,17 +4384,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E215" t="b">
         <v>1</v>
@@ -4407,36 +4403,34 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B217" t="n">
         <v>0</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E217" t="b">
         <v>1</v>
@@ -4445,17 +4439,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B218" t="n">
         <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E218" t="b">
         <v>1</v>
@@ -4464,17 +4458,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B219" t="n">
         <v>2</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.3</v>
       </c>
       <c r="E219" t="b">
         <v>1</v>
@@ -4483,34 +4477,36 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr"/>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
       <c r="C220" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D220" t="n">
         <v>-0.3</v>
       </c>
       <c r="E220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B221" t="n">
         <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D221" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E221" t="b">
         <v>1</v>
@@ -4519,32 +4515,34 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr"/>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>0</v>
+      </c>
       <c r="C222" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E223" t="b">
         <v>0</v>
@@ -4553,17 +4551,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B224" t="n">
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E224" t="b">
         <v>1</v>
@@ -4572,17 +4570,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C225" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E225" t="b">
         <v>1</v>
@@ -4591,15 +4589,15 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E226" t="b">
         <v>0</v>
@@ -4608,17 +4606,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B227" t="n">
         <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E227" t="b">
         <v>1</v>
@@ -4627,34 +4625,36 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr"/>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>-2</v>
+      </c>
       <c r="C228" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B229" t="n">
         <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E229" t="b">
         <v>1</v>
@@ -4663,36 +4663,34 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E230" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>0</v>
       </c>
       <c r="C231" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E231" t="b">
         <v>1</v>
@@ -4701,17 +4699,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B232" t="n">
         <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E232" t="b">
         <v>1</v>
@@ -4720,17 +4718,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B233" t="n">
         <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D233" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E233" t="b">
         <v>1</v>
@@ -4739,24 +4737,26 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr"/>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0</v>
+      </c>
       <c r="C234" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D234" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E235" t="b">
         <v>1</v>
@@ -4775,7 +4775,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E236" t="b">
         <v>1</v>
@@ -4794,26 +4794,24 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
       <c r="C237" t="n">
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -4823,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="D238" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E238" t="b">
         <v>1</v>
@@ -4832,7 +4830,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -4842,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E239" t="b">
         <v>1</v>
@@ -4851,7 +4849,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -4861,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="D240" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E240" t="b">
         <v>1</v>
@@ -4870,7 +4868,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -4880,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="D241" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E241" t="b">
         <v>1</v>
@@ -4889,17 +4887,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C242" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D242" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E242" t="b">
         <v>1</v>
@@ -4908,74 +4906,68 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
       <c r="C243" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D243" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D244" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E244" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="B245" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D245" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E245" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B246" t="n">
         <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D246" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E246" t="b">
         <v>1</v>
@@ -4984,36 +4976,34 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D247" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D248" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E248" t="b">
         <v>1</v>
@@ -5022,32 +5012,34 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr"/>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
       <c r="C249" t="n">
         <v>-0.8571428571428571</v>
       </c>
       <c r="D249" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D250" t="n">
-        <v>-0.3</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E250" t="b">
         <v>0</v>
@@ -5056,51 +5048,55 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr"/>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0</v>
+      </c>
       <c r="C251" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D251" t="n">
-        <v>-0.4</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>2</v>
+      </c>
       <c r="C252" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D252" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>0</v>
       </c>
       <c r="C253" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D253" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="E253" t="b">
         <v>1</v>
@@ -5109,17 +5105,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>-2.428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D254" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E254" t="b">
         <v>1</v>
@@ -5128,17 +5124,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>-2.285714285714286</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D255" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E255" t="b">
         <v>1</v>
@@ -5147,17 +5143,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>-1.857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D256" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E256" t="b">
         <v>1</v>
@@ -5166,17 +5162,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B257" t="n">
         <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>-1.428571428571429</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D257" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E257" t="b">
         <v>1</v>
@@ -5185,36 +5181,34 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B258" t="n">
-        <v>-3</v>
-      </c>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
       <c r="C258" t="n">
-        <v>-1.428571428571429</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D258" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D259" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E259" t="b">
         <v>1</v>
@@ -5223,17 +5217,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B260" t="n">
         <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D260" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E260" t="b">
         <v>1</v>
@@ -5242,17 +5236,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D261" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E261" t="b">
         <v>1</v>
@@ -5261,17 +5255,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E262" t="b">
         <v>1</v>
@@ -5280,17 +5274,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D263" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E263" t="b">
         <v>1</v>
@@ -5299,17 +5293,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B264" t="n">
         <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D264" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E264" t="b">
         <v>1</v>
@@ -5318,7 +5312,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -5328,7 +5322,7 @@
         <v>0</v>
       </c>
       <c r="D265" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E265" t="b">
         <v>1</v>
@@ -5337,7 +5331,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -5347,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="D266" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E266" t="b">
         <v>1</v>
@@ -5356,17 +5350,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C267" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D267" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E267" t="b">
         <v>1</v>
@@ -5375,17 +5369,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B268" t="n">
         <v>0</v>
       </c>
       <c r="C268" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D268" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E268" t="b">
         <v>1</v>
@@ -5394,17 +5388,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B269" t="n">
         <v>0</v>
       </c>
       <c r="C269" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D269" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E269" t="b">
         <v>1</v>
@@ -5413,17 +5407,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B270" t="n">
         <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D270" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E270" t="b">
         <v>1</v>
@@ -5432,17 +5426,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D271" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E271" t="b">
         <v>1</v>
@@ -5451,36 +5445,34 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="B272" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D272" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B273" t="n">
         <v>0</v>
       </c>
       <c r="C273" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E273" t="b">
         <v>1</v>
@@ -5489,7 +5481,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -5499,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="D274" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E274" t="b">
         <v>1</v>
@@ -5508,7 +5500,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -5518,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="D275" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E275" t="b">
         <v>1</v>
@@ -5527,7 +5519,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -5537,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="D276" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E276" t="b">
         <v>1</v>
@@ -5546,7 +5538,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -5556,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="D277" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E277" t="b">
         <v>1</v>
@@ -5565,7 +5557,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -5575,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="D278" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E278" t="b">
         <v>1</v>
@@ -5584,7 +5576,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -5594,7 +5586,7 @@
         <v>0</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E279" t="b">
         <v>1</v>
@@ -5603,24 +5595,26 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr"/>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0</v>
+      </c>
       <c r="C280" t="n">
         <v>0</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -5630,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="D281" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E281" t="b">
         <v>1</v>
@@ -5639,7 +5633,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -5649,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="D282" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E282" t="b">
         <v>1</v>
@@ -5658,7 +5652,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -5668,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="D283" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E283" t="b">
         <v>1</v>
@@ -5677,70 +5671,72 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr"/>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>-3</v>
+      </c>
       <c r="C284" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D284" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E284" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr"/>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0</v>
+      </c>
       <c r="C285" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D285" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B286" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
       <c r="C286" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D286" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>0</v>
       </c>
       <c r="C287" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D287" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E287" t="b">
         <v>1</v>
@@ -5749,34 +5745,36 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr"/>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
       <c r="C288" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E288" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B289" t="n">
         <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E289" t="b">
         <v>1</v>
@@ -5785,17 +5783,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B290" t="n">
         <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E290" t="b">
         <v>1</v>
@@ -5804,17 +5802,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C291" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D291" t="n">
-        <v>0</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E291" t="b">
         <v>1</v>
@@ -5823,17 +5821,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="B292" t="n">
         <v>-2</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D292" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E292" t="b">
         <v>1</v>
@@ -5842,85 +5840,93 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr"/>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0</v>
+      </c>
       <c r="C293" t="n">
         <v>-0.5714285714285714</v>
       </c>
       <c r="D293" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E293" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr"/>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0</v>
+      </c>
       <c r="C294" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D294" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E294" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr"/>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0</v>
+      </c>
       <c r="C295" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D295" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E295" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr"/>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-2</v>
+      </c>
       <c r="C296" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D296" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E296" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="C297" t="n">
-        <v>-1.714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D297" t="n">
-        <v>-0.4</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E297" t="b">
         <v>1</v>
@@ -5929,17 +5935,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>-2</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D298" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E298" t="b">
         <v>1</v>
@@ -5948,17 +5954,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="B299" t="n">
         <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D299" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E299" t="b">
         <v>1</v>
@@ -5967,17 +5973,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="B300" t="n">
         <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>-1.428571428571429</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D300" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E300" t="b">
         <v>1</v>
@@ -5986,17 +5992,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B301" t="n">
         <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D301" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E301" t="b">
         <v>1</v>
@@ -6005,17 +6011,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B302" t="n">
         <v>0</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D302" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E302" t="b">
         <v>1</v>
@@ -6024,34 +6030,36 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr"/>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>0</v>
+      </c>
       <c r="C303" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D303" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E303" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E304" t="b">
         <v>1</v>
@@ -6060,17 +6068,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D305" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E305" t="b">
         <v>1</v>
@@ -6079,34 +6087,1742 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr"/>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>0</v>
+      </c>
       <c r="C306" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D306" t="n">
-        <v>-0.6</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E306" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0</v>
+      </c>
+      <c r="C307" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D307" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E307" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0</v>
+      </c>
+      <c r="C308" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D308" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E308" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0</v>
+      </c>
+      <c r="C309" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D309" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E309" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>2</v>
+      </c>
+      <c r="C310" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="D310" t="n">
+        <v>-0.3666666666666666</v>
+      </c>
+      <c r="E310" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+      <c r="C311" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D311" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E311" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>0</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D312" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E312" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+      <c r="C313" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D313" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E313" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+      <c r="C314" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D314" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E314" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>0</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D315" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E315" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>0</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="D316" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E316" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D317" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E317" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>0</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0</v>
+      </c>
+      <c r="D318" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E318" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" t="n">
+        <v>0</v>
+      </c>
+      <c r="D319" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E319" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>0</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E320" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>0</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E321" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>0</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0</v>
+      </c>
+      <c r="D322" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E322" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>0</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E323" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>0</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E324" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr"/>
+      <c r="C325" t="n">
+        <v>0</v>
+      </c>
+      <c r="D325" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E325" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E327" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>0</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E328" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E329" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>0</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E330" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E331" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>0</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E332" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>0</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E333" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>0</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E334" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>0</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E335" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>0</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E336" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>0</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E337" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>0</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="E338" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C339" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="E339" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D340" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E340" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="D341" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E341" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D342" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E342" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D343" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E343" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>0</v>
+      </c>
+      <c r="C344" t="n">
+        <v>-2.142857142857143</v>
+      </c>
+      <c r="D344" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E344" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C345" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D345" t="n">
+        <v>-0.5666666666666667</v>
+      </c>
+      <c r="E345" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C346" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="D346" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E346" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>0</v>
+      </c>
+      <c r="C347" t="n">
+        <v>-1.857142857142857</v>
+      </c>
+      <c r="D347" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E347" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0</v>
+      </c>
+      <c r="C348" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D348" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E348" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C349" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D349" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E349" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0</v>
+      </c>
+      <c r="C350" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D350" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E350" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0</v>
+      </c>
+      <c r="C351" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D351" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E351" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0</v>
+      </c>
+      <c r="C352" t="n">
+        <v>-0.7142857142857143</v>
+      </c>
+      <c r="D352" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E352" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0</v>
+      </c>
+      <c r="C353" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D353" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E353" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0</v>
+      </c>
+      <c r="C354" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D354" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E354" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0</v>
+      </c>
+      <c r="C355" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D355" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E355" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0</v>
+      </c>
+      <c r="D356" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E356" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0</v>
+      </c>
+      <c r="D357" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E357" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0</v>
+      </c>
+      <c r="D358" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E358" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0</v>
+      </c>
+      <c r="D359" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E359" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0</v>
+      </c>
+      <c r="D360" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E360" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0</v>
+      </c>
+      <c r="D361" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E361" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0</v>
+      </c>
+      <c r="D362" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E362" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0</v>
+      </c>
+      <c r="D363" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E363" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0</v>
+      </c>
+      <c r="D364" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E364" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0</v>
+      </c>
+      <c r="D365" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E365" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>0</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0</v>
+      </c>
+      <c r="D366" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E366" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0</v>
+      </c>
+      <c r="D367" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E367" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0</v>
+      </c>
+      <c r="D368" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E368" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0</v>
+      </c>
+      <c r="D369" t="n">
+        <v>-0.6333333333333333</v>
+      </c>
+      <c r="E369" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0</v>
+      </c>
+      <c r="D370" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E370" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="n">
+        <v>0</v>
+      </c>
+      <c r="D371" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E371" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0</v>
+      </c>
+      <c r="D372" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E372" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0</v>
+      </c>
+      <c r="D373" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E373" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>0</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0</v>
+      </c>
+      <c r="D374" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E374" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="n">
+        <v>0</v>
+      </c>
+      <c r="D375" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="E375" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="n">
+        <v>0</v>
+      </c>
+      <c r="D376" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E376" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>0</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0</v>
+      </c>
+      <c r="D377" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E377" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0</v>
+      </c>
+      <c r="D378" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E378" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="n">
+        <v>0</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>0</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>0</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>0</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0</v>
+      </c>
+      <c r="E382" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C383" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D383" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E383" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D384" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E384" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D385" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E385" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D386" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="E386" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+      <c r="C387" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D387" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E387" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C388" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D388" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E388" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C389" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D389" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E389" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>0</v>
+      </c>
+      <c r="C390" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D390" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E390" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>0</v>
+      </c>
+      <c r="C391" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D391" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E391" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>0</v>
+      </c>
+      <c r="C392" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D392" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E392" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>0</v>
+      </c>
+      <c r="C393" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D393" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E393" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D394" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E394" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>0</v>
+      </c>
+      <c r="C395" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D395" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E395" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C396" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D396" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E396" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D397" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E397" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr"/>
-      <c r="C307" t="n">
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="n">
         <v>-0.8571428571428571</v>
       </c>
-      <c r="D307" t="n">
+      <c r="D398" t="n">
         <v>-0.6666666666666666</v>
       </c>
-      <c r="E307" t="b">
+      <c r="E398" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D399" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E399" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6140,7 +7856,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-05-21 to 2026-03-22 | Publication days: 259</t>
+          <t>Coverage: 2025-02-19 to 2026-03-23 | Publication days: 335</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7823,6 +7823,23 @@
         <v>-0.7333333333333333</v>
       </c>
       <c r="E399" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D400" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E400" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7856,7 +7873,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-02-19 to 2026-03-23 | Publication days: 335</t>
+          <t>Coverage: 2025-02-19 to 2026-03-24 | Publication days: 335</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:E401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7840,6 +7840,23 @@
         <v>-0.8</v>
       </c>
       <c r="E400" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D401" t="n">
+        <v>-0.8666666666666667</v>
+      </c>
+      <c r="E401" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7873,7 +7890,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-02-19 to 2026-03-24 | Publication days: 335</t>
+          <t>Coverage: 2025-02-19 to 2026-03-25 | Publication days: 335</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:E431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -463,11 +463,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -478,123 +478,109 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>0.4285714285714285</v>
+        <v>-2</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0.4285714285714285</v>
+        <v>-2</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4285714285714285</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
@@ -604,46 +590,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0.4285714285714285</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>0.4285714285714285</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="b">
@@ -653,75 +635,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -738,240 +712,214 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>-3</v>
-      </c>
+          <t>2025-02-16</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -980,17 +928,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
@@ -999,51 +947,55 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
       <c r="C34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
@@ -1052,17 +1004,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -1071,17 +1023,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -1090,17 +1042,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
@@ -1109,17 +1061,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
@@ -1128,70 +1080,72 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
       <c r="C41" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="E41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
       <c r="C42" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="E42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="E43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3666666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
@@ -1200,17 +1154,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
@@ -1219,17 +1173,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -1238,17 +1192,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
@@ -1257,17 +1211,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
@@ -1276,17 +1230,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E49" t="b">
         <v>1</v>
@@ -1295,17 +1249,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E50" t="b">
         <v>1</v>
@@ -1314,17 +1268,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E51" t="b">
         <v>1</v>
@@ -1333,17 +1287,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E52" t="b">
         <v>1</v>
@@ -1352,17 +1306,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E53" t="b">
         <v>1</v>
@@ -1371,7 +1325,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1381,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5666666666666667</v>
+        <v>0.1</v>
       </c>
       <c r="E54" t="b">
         <v>1</v>
@@ -1390,51 +1344,55 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-2</v>
+      </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E57" t="b">
         <v>1</v>
@@ -1443,17 +1401,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E58" t="b">
         <v>1</v>
@@ -1462,17 +1420,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E59" t="b">
         <v>1</v>
@@ -1481,17 +1439,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.4</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E60" t="b">
         <v>1</v>
@@ -1500,17 +1458,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.4</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E61" t="b">
         <v>1</v>
@@ -1519,17 +1477,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E62" t="b">
         <v>1</v>
@@ -1538,17 +1496,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E63" t="b">
         <v>1</v>
@@ -1557,55 +1515,51 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>-3</v>
-      </c>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
         <v>-0.7142857142857143</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E66" t="b">
         <v>1</v>
@@ -1614,34 +1568,36 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E68" t="b">
         <v>1</v>
@@ -1650,89 +1606,89 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>-2</v>
+      </c>
       <c r="C69" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
       <c r="C70" t="n">
-        <v>-1.571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-1.285714285714286</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E73" t="b">
         <v>1</v>
@@ -1741,7 +1697,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1751,7 +1707,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E74" t="b">
         <v>1</v>
@@ -1760,7 +1716,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1770,7 +1726,7 @@
         <v>-0.5714285714285714</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E75" t="b">
         <v>1</v>
@@ -1779,17 +1735,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>-2</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E76" t="b">
         <v>1</v>
@@ -1798,34 +1754,36 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>-2</v>
+      </c>
       <c r="C77" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.571428571428571</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E78" t="b">
         <v>1</v>
@@ -1834,17 +1792,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E79" t="b">
         <v>1</v>
@@ -1853,17 +1811,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>-2</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.9</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E80" t="b">
         <v>1</v>
@@ -1872,17 +1830,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.428571428571428</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D81" t="n">
-        <v>-1</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E81" t="b">
         <v>1</v>
@@ -1891,17 +1849,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>-2.571428571428572</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.1</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E82" t="b">
         <v>1</v>
@@ -1910,89 +1868,89 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
       <c r="C83" t="n">
-        <v>-2.714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.2</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
       <c r="C84" t="n">
-        <v>-2.857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>-1.3</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>-2.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>-1.366666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>-2.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>-1.366666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>-1.366666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E87" t="b">
         <v>1</v>
@@ -2001,51 +1959,55 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
       <c r="C88" t="n">
-        <v>-1.571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>-1.366666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
       <c r="C89" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>-1.366666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E90" t="b">
         <v>1</v>
@@ -2054,7 +2016,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2064,7 +2026,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D91" t="n">
-        <v>-1.3</v>
+        <v>-0.4</v>
       </c>
       <c r="E91" t="b">
         <v>1</v>
@@ -2073,17 +2035,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D92" t="n">
-        <v>-1.3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E92" t="b">
         <v>1</v>
@@ -2092,17 +2054,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.466666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E93" t="b">
         <v>1</v>
@@ -2111,17 +2073,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D94" t="n">
-        <v>-1.5</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E94" t="b">
         <v>1</v>
@@ -2130,17 +2092,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D95" t="n">
-        <v>-1.4</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E95" t="b">
         <v>1</v>
@@ -2149,17 +2111,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D96" t="n">
-        <v>-1.3</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E96" t="b">
         <v>1</v>
@@ -2168,36 +2130,34 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.2</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.2</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E98" t="b">
         <v>1</v>
@@ -2206,55 +2166,51 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D99" t="n">
-        <v>-1.2</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.2</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.2</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E101" t="b">
         <v>1</v>
@@ -2263,17 +2219,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D102" t="n">
-        <v>-1.133333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E102" t="b">
         <v>1</v>
@@ -2282,17 +2238,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B103" t="n">
         <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.133333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E103" t="b">
         <v>1</v>
@@ -2301,17 +2257,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.133333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E104" t="b">
         <v>1</v>
@@ -2320,17 +2276,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.066666666666667</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E105" t="b">
         <v>1</v>
@@ -2339,17 +2295,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D106" t="n">
-        <v>-1</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E106" t="b">
         <v>1</v>
@@ -2358,36 +2314,34 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.9333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E108" t="b">
         <v>1</v>
@@ -2396,17 +2350,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E109" t="b">
         <v>1</v>
@@ -2415,17 +2369,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>-2</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-2</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E110" t="b">
         <v>1</v>
@@ -2434,17 +2388,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-2.428571428571428</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="E111" t="b">
         <v>1</v>
@@ -2453,32 +2407,34 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>-3</v>
+      </c>
       <c r="C112" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-1.1</v>
       </c>
       <c r="E112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-2.714285714285714</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-1.2</v>
       </c>
       <c r="E113" t="b">
         <v>0</v>
@@ -2487,36 +2443,34 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>-3</v>
-      </c>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-2.857142857142857</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-1.3</v>
       </c>
       <c r="E114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-2.714285714285714</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E115" t="b">
         <v>1</v>
@@ -2525,17 +2479,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>-1</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E116" t="b">
         <v>1</v>
@@ -2544,17 +2498,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B117" t="n">
         <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-2</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E117" t="b">
         <v>1</v>
@@ -2563,55 +2517,51 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>-1</v>
+        <v>-1.571428571428571</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.5</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>-1</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.5</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>-1</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="E120" t="b">
         <v>1</v>
@@ -2620,17 +2570,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-1.3</v>
       </c>
       <c r="E121" t="b">
         <v>1</v>
@@ -2639,17 +2589,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-1.3</v>
       </c>
       <c r="E122" t="b">
         <v>1</v>
@@ -2658,17 +2608,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-1.466666666666667</v>
       </c>
       <c r="E123" t="b">
         <v>1</v>
@@ -2677,34 +2627,36 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>-3</v>
+      </c>
       <c r="C124" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-1.5</v>
       </c>
       <c r="E124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="E125" t="b">
         <v>1</v>
@@ -2713,17 +2665,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.4</v>
+        <v>-1.3</v>
       </c>
       <c r="E126" t="b">
         <v>1</v>
@@ -2732,17 +2684,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="E127" t="b">
         <v>1</v>
@@ -2751,17 +2703,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="E128" t="b">
         <v>1</v>
@@ -2770,17 +2722,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="E129" t="b">
         <v>1</v>
@@ -2789,17 +2741,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="E130" t="b">
         <v>1</v>
@@ -2808,34 +2760,36 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
       <c r="C131" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="E131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B132" t="n">
         <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>-1.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.6</v>
+        <v>-1.133333333333333</v>
       </c>
       <c r="E132" t="b">
         <v>1</v>
@@ -2844,17 +2798,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-1.133333333333333</v>
       </c>
       <c r="E133" t="b">
         <v>1</v>
@@ -2863,17 +2817,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-1.133333333333333</v>
       </c>
       <c r="E134" t="b">
         <v>1</v>
@@ -2882,17 +2836,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>-1.857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="E135" t="b">
         <v>1</v>
@@ -2901,17 +2855,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>-1.857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-1</v>
       </c>
       <c r="E136" t="b">
         <v>1</v>
@@ -2920,17 +2874,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>-1.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.9</v>
+        <v>-0.9333333333333333</v>
       </c>
       <c r="E137" t="b">
         <v>1</v>
@@ -2939,17 +2893,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B138" t="n">
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>-1.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.9</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E138" t="b">
         <v>1</v>
@@ -2958,17 +2912,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>-1.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.9</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E139" t="b">
         <v>1</v>
@@ -2977,17 +2931,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C140" t="n">
-        <v>-1</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E140" t="b">
         <v>1</v>
@@ -2996,17 +2950,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>-1</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.9</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E141" t="b">
         <v>1</v>
@@ -3015,55 +2969,51 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.9</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.9</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.8</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E144" t="b">
         <v>1</v>
@@ -3072,17 +3022,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.8</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E145" t="b">
         <v>1</v>
@@ -3091,17 +3041,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E146" t="b">
         <v>1</v>
@@ -3110,17 +3060,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.8</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E147" t="b">
         <v>1</v>
@@ -3129,17 +3079,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E148" t="b">
         <v>1</v>
@@ -3148,17 +3098,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E149" t="b">
         <v>1</v>
@@ -3167,17 +3117,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="B150" t="n">
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E150" t="b">
         <v>1</v>
@@ -3186,17 +3136,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E151" t="b">
         <v>1</v>
@@ -3205,34 +3155,36 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
       <c r="C152" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="B153" t="n">
         <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E153" t="b">
         <v>1</v>
@@ -3241,15 +3193,15 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E154" t="b">
         <v>0</v>
@@ -3258,17 +3210,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E155" t="b">
         <v>1</v>
@@ -3277,17 +3229,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E156" t="b">
         <v>1</v>
@@ -3296,17 +3248,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="E157" t="b">
         <v>1</v>
@@ -3315,17 +3267,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="E158" t="b">
         <v>1</v>
@@ -3334,17 +3286,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="E159" t="b">
         <v>1</v>
@@ -3353,53 +3305,53 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>-3</v>
+      </c>
       <c r="C160" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="E160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="E162" t="b">
         <v>1</v>
@@ -3408,17 +3360,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E163" t="b">
         <v>1</v>
@@ -3427,17 +3379,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>-2</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E164" t="b">
         <v>1</v>
@@ -3446,17 +3398,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.4</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E165" t="b">
         <v>1</v>
@@ -3465,17 +3417,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.4</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E166" t="b">
         <v>1</v>
@@ -3484,17 +3436,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E167" t="b">
         <v>1</v>
@@ -3503,17 +3455,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E168" t="b">
         <v>1</v>
@@ -3522,17 +3474,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E169" t="b">
         <v>1</v>
@@ -3541,17 +3493,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-1</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="E170" t="b">
         <v>1</v>
@@ -3560,17 +3512,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-1</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.9</v>
       </c>
       <c r="E171" t="b">
         <v>1</v>
@@ -3579,17 +3531,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E172" t="b">
         <v>1</v>
@@ -3598,17 +3550,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.9</v>
       </c>
       <c r="E173" t="b">
         <v>1</v>
@@ -3617,34 +3569,36 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr"/>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
       <c r="C174" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.8</v>
       </c>
       <c r="E174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.8</v>
       </c>
       <c r="E175" t="b">
         <v>1</v>
@@ -3653,17 +3607,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E176" t="b">
         <v>1</v>
@@ -3672,17 +3626,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C177" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.8</v>
       </c>
       <c r="E177" t="b">
         <v>1</v>
@@ -3691,17 +3645,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>0.1428571428571428</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E178" t="b">
         <v>1</v>
@@ -3710,34 +3664,36 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr"/>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
       <c r="C179" t="n">
-        <v>0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E180" t="b">
         <v>1</v>
@@ -3746,17 +3702,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E181" t="b">
         <v>1</v>
@@ -3765,36 +3721,34 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E183" t="b">
         <v>1</v>
@@ -3803,36 +3757,34 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E185" t="b">
         <v>1</v>
@@ -3841,17 +3793,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E186" t="b">
         <v>1</v>
@@ -3860,41 +3812,45 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr"/>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>-2</v>
+      </c>
       <c r="C187" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr"/>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
       <c r="C188" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3904,7 +3860,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.7</v>
       </c>
       <c r="E189" t="b">
         <v>1</v>
@@ -3913,36 +3869,34 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.6</v>
       </c>
       <c r="E190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E191" t="b">
         <v>1</v>
@@ -3951,7 +3905,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3961,7 +3915,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E192" t="b">
         <v>1</v>
@@ -3970,7 +3924,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -3980,7 +3934,7 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E193" t="b">
         <v>1</v>
@@ -3989,17 +3943,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C194" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E194" t="b">
         <v>1</v>
@@ -4008,17 +3962,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E195" t="b">
         <v>1</v>
@@ -4027,17 +3981,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="E196" t="b">
         <v>1</v>
@@ -4046,17 +4000,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E197" t="b">
         <v>1</v>
@@ -4065,17 +4019,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E198" t="b">
         <v>1</v>
@@ -4084,17 +4038,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E199" t="b">
         <v>1</v>
@@ -4103,17 +4057,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="B200" t="n">
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E200" t="b">
         <v>1</v>
@@ -4122,17 +4076,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E201" t="b">
         <v>1</v>
@@ -4141,31 +4095,33 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>-2</v>
+      </c>
       <c r="C202" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C203" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D203" t="n">
         <v>-0.2333333333333333</v>
@@ -4177,36 +4133,34 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>-2</v>
-      </c>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.4</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.3</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E205" t="b">
         <v>1</v>
@@ -4215,17 +4169,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E206" t="b">
         <v>1</v>
@@ -4234,17 +4188,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E207" t="b">
         <v>1</v>
@@ -4253,17 +4207,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B208" t="n">
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E208" t="b">
         <v>1</v>
@@ -4272,15 +4226,15 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E209" t="b">
         <v>0</v>
@@ -4289,17 +4243,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="B210" t="n">
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E210" t="b">
         <v>1</v>
@@ -4308,17 +4262,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="B211" t="n">
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D211" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E211" t="b">
         <v>1</v>
@@ -4327,17 +4281,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B212" t="n">
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E212" t="b">
         <v>1</v>
@@ -4346,17 +4300,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E213" t="b">
         <v>1</v>
@@ -4365,7 +4319,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -4375,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E214" t="b">
         <v>1</v>
@@ -4384,17 +4338,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C215" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E215" t="b">
         <v>1</v>
@@ -4403,72 +4357,70 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr"/>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>0</v>
+      </c>
       <c r="C216" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E219" t="b">
         <v>1</v>
@@ -4477,17 +4429,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B220" t="n">
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.3</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E220" t="b">
         <v>1</v>
@@ -4496,14 +4448,14 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C221" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D221" t="n">
         <v>-0.2333333333333333</v>
@@ -4515,14 +4467,14 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B222" t="n">
         <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D222" t="n">
         <v>-0.2333333333333333</v>
@@ -4534,34 +4486,36 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr"/>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>0</v>
+      </c>
       <c r="C223" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D223" t="n">
         <v>-0.2333333333333333</v>
       </c>
       <c r="E223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B224" t="n">
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E224" t="b">
         <v>1</v>
@@ -4570,17 +4524,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E225" t="b">
         <v>1</v>
@@ -4589,34 +4543,36 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr"/>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>-3</v>
+      </c>
       <c r="C226" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B227" t="n">
         <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E227" t="b">
         <v>1</v>
@@ -4625,17 +4581,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E228" t="b">
         <v>1</v>
@@ -4644,17 +4600,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B229" t="n">
         <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E229" t="b">
         <v>1</v>
@@ -4663,34 +4619,36 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr"/>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
       <c r="C230" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>0</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E231" t="b">
         <v>1</v>
@@ -4699,36 +4657,34 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
       <c r="C232" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B233" t="n">
         <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E233" t="b">
         <v>1</v>
@@ -4737,17 +4693,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C234" t="n">
         <v>-0.2857142857142857</v>
       </c>
       <c r="D234" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="E234" t="b">
         <v>1</v>
@@ -4756,17 +4712,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B235" t="n">
         <v>0</v>
       </c>
       <c r="C235" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D235" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E235" t="b">
         <v>1</v>
@@ -4775,17 +4731,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C236" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D236" t="n">
-        <v>-0.2</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E236" t="b">
         <v>1</v>
@@ -4794,34 +4750,36 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr"/>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>-2</v>
+      </c>
       <c r="C237" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D237" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B238" t="n">
         <v>0</v>
       </c>
       <c r="C238" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D238" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E238" t="b">
         <v>1</v>
@@ -4830,36 +4788,34 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="B239" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D239" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E239" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B240" t="n">
         <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D240" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E240" t="b">
         <v>1</v>
@@ -4868,17 +4824,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B241" t="n">
         <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E241" t="b">
         <v>1</v>
@@ -4887,17 +4843,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D242" t="n">
-        <v>-0.2</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E242" t="b">
         <v>1</v>
@@ -4906,104 +4862,110 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr"/>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
       <c r="C243" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D243" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr"/>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0</v>
+      </c>
       <c r="C244" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr"/>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0</v>
+      </c>
       <c r="C245" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="B246" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D246" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr"/>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
       <c r="C247" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D247" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B248" t="n">
         <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D248" t="n">
-        <v>-0.4</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E248" t="b">
         <v>1</v>
@@ -5012,17 +4974,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D249" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E249" t="b">
         <v>1</v>
@@ -5031,34 +4993,36 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr"/>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
       <c r="C250" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D250" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.3</v>
       </c>
       <c r="E250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B251" t="n">
         <v>0</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D251" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E251" t="b">
         <v>1</v>
@@ -5067,17 +5031,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C252" t="n">
         <v>0.2857142857142857</v>
       </c>
       <c r="D252" t="n">
-        <v>-0.4</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E252" t="b">
         <v>1</v>
@@ -5086,26 +5050,24 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="n">
         <v>0.2857142857142857</v>
       </c>
       <c r="D253" t="n">
-        <v>-0.4</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -5115,7 +5077,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="D254" t="n">
-        <v>-0.4</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E254" t="b">
         <v>1</v>
@@ -5124,17 +5086,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C255" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D255" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E255" t="b">
         <v>1</v>
@@ -5143,33 +5105,31 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="B256" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D256" t="n">
         <v>-0.2666666666666667</v>
       </c>
       <c r="E256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B257" t="n">
         <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D257" t="n">
         <v>-0.2666666666666667</v>
@@ -5181,34 +5141,36 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr"/>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>-2</v>
+      </c>
       <c r="C258" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D258" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D259" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E259" t="b">
         <v>1</v>
@@ -5217,36 +5179,34 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
       <c r="C260" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D260" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E260" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D261" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E261" t="b">
         <v>1</v>
@@ -5255,17 +5215,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E262" t="b">
         <v>1</v>
@@ -5274,17 +5234,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D263" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E263" t="b">
         <v>1</v>
@@ -5293,17 +5253,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B264" t="n">
         <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D264" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E264" t="b">
         <v>1</v>
@@ -5312,7 +5272,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -5322,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="D265" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E265" t="b">
         <v>1</v>
@@ -5331,7 +5291,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -5350,36 +5310,34 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="B267" t="n">
-        <v>-3</v>
-      </c>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D267" t="n">
-        <v>-0.3</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E267" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B268" t="n">
         <v>0</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D268" t="n">
-        <v>-0.3</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E268" t="b">
         <v>1</v>
@@ -5388,17 +5346,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B269" t="n">
         <v>0</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D269" t="n">
-        <v>-0.3</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E269" t="b">
         <v>1</v>
@@ -5407,17 +5365,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B270" t="n">
         <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D270" t="n">
-        <v>-0.3</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E270" t="b">
         <v>1</v>
@@ -5426,17 +5384,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D271" t="n">
-        <v>-0.3</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E271" t="b">
         <v>1</v>
@@ -5445,91 +5403,87 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr"/>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>-2</v>
+      </c>
       <c r="C272" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D272" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D274" t="n">
-        <v>-0.1</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E274" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="B275" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D275" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E275" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B276" t="n">
         <v>0</v>
       </c>
       <c r="C276" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D276" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E276" t="b">
         <v>1</v>
@@ -5538,36 +5492,34 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
       <c r="C277" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D277" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E277" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B278" t="n">
         <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>0</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D278" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E278" t="b">
         <v>1</v>
@@ -5576,17 +5528,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E279" t="b">
         <v>1</v>
@@ -5595,36 +5547,34 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="B280" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
       <c r="C280" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B281" t="n">
         <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D281" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="E281" t="b">
         <v>1</v>
@@ -5633,17 +5583,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C282" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D282" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E282" t="b">
         <v>1</v>
@@ -5652,17 +5602,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B283" t="n">
         <v>0</v>
       </c>
       <c r="C283" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D283" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E283" t="b">
         <v>1</v>
@@ -5671,17 +5621,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D284" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="E284" t="b">
         <v>1</v>
@@ -5690,17 +5640,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B285" t="n">
         <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D285" t="n">
-        <v>-0.2</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E285" t="b">
         <v>1</v>
@@ -5709,34 +5659,36 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr"/>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0</v>
+      </c>
       <c r="C286" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D286" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>0</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D287" t="n">
-        <v>-0.2</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E287" t="b">
         <v>1</v>
@@ -5745,33 +5697,31 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="B288" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D288" t="n">
         <v>-0.2</v>
       </c>
       <c r="E288" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B289" t="n">
         <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D289" t="n">
         <v>-0.2</v>
@@ -5783,14 +5733,14 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B290" t="n">
         <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D290" t="n">
         <v>-0.2</v>
@@ -5802,17 +5752,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D291" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E291" t="b">
         <v>1</v>
@@ -5821,17 +5771,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D292" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E292" t="b">
         <v>1</v>
@@ -5840,17 +5790,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B293" t="n">
         <v>0</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E293" t="b">
         <v>1</v>
@@ -5859,17 +5809,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B294" t="n">
         <v>0</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D294" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E294" t="b">
         <v>1</v>
@@ -5878,17 +5828,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B295" t="n">
         <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D295" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E295" t="b">
         <v>1</v>
@@ -5897,17 +5847,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D296" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E296" t="b">
         <v>1</v>
@@ -5916,17 +5866,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="C297" t="n">
-        <v>-1</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D297" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E297" t="b">
         <v>1</v>
@@ -5935,17 +5885,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B298" t="n">
         <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.7142857142857143</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D298" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E298" t="b">
         <v>1</v>
@@ -5954,7 +5904,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -5964,7 +5914,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D299" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E299" t="b">
         <v>1</v>
@@ -5973,7 +5923,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -5983,7 +5933,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D300" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E300" t="b">
         <v>1</v>
@@ -5992,7 +5942,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -6002,7 +5952,7 @@
         <v>-0.4285714285714285</v>
       </c>
       <c r="D301" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E301" t="b">
         <v>1</v>
@@ -6011,36 +5961,34 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="B302" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
         <v>-0.4285714285714285</v>
       </c>
       <c r="D302" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.2333333333333333</v>
       </c>
       <c r="E302" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B303" t="n">
         <v>0</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.1428571428571428</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D303" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="E303" t="b">
         <v>1</v>
@@ -6049,17 +5997,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.1</v>
       </c>
       <c r="E304" t="b">
         <v>1</v>
@@ -6068,17 +6016,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B305" t="n">
         <v>0</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D305" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E305" t="b">
         <v>1</v>
@@ -6087,17 +6035,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B306" t="n">
         <v>0</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D306" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E306" t="b">
         <v>1</v>
@@ -6106,17 +6054,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B307" t="n">
         <v>0</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D307" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E307" t="b">
         <v>1</v>
@@ -6125,17 +6073,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B308" t="n">
         <v>0</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D308" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E308" t="b">
         <v>1</v>
@@ -6144,17 +6092,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="B309" t="n">
         <v>0</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D309" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E309" t="b">
         <v>1</v>
@@ -6163,17 +6111,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="D310" t="n">
-        <v>-0.3666666666666666</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E310" t="b">
         <v>1</v>
@@ -6182,34 +6130,36 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr"/>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0</v>
+      </c>
       <c r="C311" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D311" t="n">
-        <v>-0.3</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="E311" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B312" t="n">
         <v>0</v>
       </c>
       <c r="C312" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E312" t="b">
         <v>1</v>
@@ -6218,48 +6168,52 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr"/>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
       <c r="C313" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D313" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E313" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr"/>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>-3</v>
+      </c>
       <c r="C314" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D314" t="n">
         <v>-0.2</v>
       </c>
       <c r="E314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="B315" t="n">
         <v>0</v>
       </c>
       <c r="C315" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D315" t="n">
         <v>-0.2</v>
@@ -6271,50 +6225,50 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="B316" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
-        <v>0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D316" t="n">
         <v>-0.2</v>
       </c>
       <c r="E316" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr"/>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>0</v>
+      </c>
       <c r="C317" t="n">
-        <v>0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D317" t="n">
         <v>-0.2</v>
       </c>
       <c r="E317" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B318" t="n">
         <v>0</v>
       </c>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D318" t="n">
         <v>-0.2</v>
@@ -6326,31 +6280,33 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr"/>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>0</v>
+      </c>
       <c r="C319" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D319" t="n">
         <v>-0.2</v>
       </c>
       <c r="E319" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B320" t="n">
         <v>0</v>
       </c>
       <c r="C320" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D320" t="n">
         <v>-0.2</v>
@@ -6362,17 +6318,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C321" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D321" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.2666666666666667</v>
       </c>
       <c r="E321" t="b">
         <v>1</v>
@@ -6381,17 +6337,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C322" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D322" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E322" t="b">
         <v>1</v>
@@ -6400,17 +6356,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="B323" t="n">
         <v>0</v>
       </c>
       <c r="C323" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D323" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E323" t="b">
         <v>1</v>
@@ -6419,17 +6375,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B324" t="n">
         <v>0</v>
       </c>
       <c r="C324" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D324" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E324" t="b">
         <v>1</v>
@@ -6438,34 +6394,36 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr"/>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0</v>
+      </c>
       <c r="C325" t="n">
-        <v>0</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D325" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E325" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C326" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="E326" t="b">
         <v>1</v>
@@ -6474,17 +6432,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C327" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D327" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E327" t="b">
         <v>1</v>
@@ -6493,17 +6451,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B328" t="n">
         <v>0</v>
       </c>
       <c r="C328" t="n">
-        <v>0</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D328" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E328" t="b">
         <v>1</v>
@@ -6512,17 +6470,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="B329" t="n">
         <v>0</v>
       </c>
       <c r="C329" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D329" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E329" t="b">
         <v>1</v>
@@ -6531,17 +6489,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="B330" t="n">
         <v>0</v>
       </c>
       <c r="C330" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D330" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E330" t="b">
         <v>1</v>
@@ -6550,17 +6508,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B331" t="n">
         <v>0</v>
       </c>
       <c r="C331" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D331" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E331" t="b">
         <v>1</v>
@@ -6569,17 +6527,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B332" t="n">
         <v>0</v>
       </c>
       <c r="C332" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D332" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E332" t="b">
         <v>1</v>
@@ -6588,17 +6546,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B333" t="n">
         <v>0</v>
       </c>
       <c r="C333" t="n">
-        <v>0</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D333" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E333" t="b">
         <v>1</v>
@@ -6607,17 +6565,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C334" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D334" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E334" t="b">
         <v>1</v>
@@ -6626,17 +6584,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B335" t="n">
         <v>0</v>
       </c>
       <c r="C335" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D335" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E335" t="b">
         <v>1</v>
@@ -6645,17 +6603,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="B336" t="n">
         <v>0</v>
       </c>
       <c r="C336" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D336" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E336" t="b">
         <v>1</v>
@@ -6664,17 +6622,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="B337" t="n">
         <v>0</v>
       </c>
       <c r="C337" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D337" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E337" t="b">
         <v>1</v>
@@ -6683,17 +6641,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B338" t="n">
         <v>0</v>
       </c>
       <c r="C338" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D338" t="n">
-        <v>0.1333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E338" t="b">
         <v>1</v>
@@ -6702,17 +6660,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="C339" t="n">
         <v>-0.4285714285714285</v>
       </c>
       <c r="D339" t="n">
-        <v>0.03333333333333333</v>
+        <v>-0.4333333333333333</v>
       </c>
       <c r="E339" t="b">
         <v>1</v>
@@ -6721,29 +6679,31 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr"/>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>2</v>
+      </c>
       <c r="C340" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D340" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.3666666666666666</v>
       </c>
       <c r="E340" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
-        <v>-1.285714285714286</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D341" t="n">
         <v>-0.3</v>
@@ -6755,32 +6715,34 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr"/>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>0</v>
+      </c>
       <c r="C342" t="n">
-        <v>-1.714285714285714</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="E342" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D343" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="E343" t="b">
         <v>0</v>
@@ -6789,36 +6751,34 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
-        </is>
-      </c>
-      <c r="B344" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
-        <v>-2.142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D344" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="E344" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C345" t="n">
-        <v>-2.428571428571428</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D345" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.2</v>
       </c>
       <c r="E345" t="b">
         <v>1</v>
@@ -6827,17 +6787,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C346" t="n">
-        <v>-2.285714285714286</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D346" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E346" t="b">
         <v>1</v>
@@ -6846,36 +6806,34 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="B347" t="n">
-        <v>0</v>
-      </c>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="n">
-        <v>-1.857142857142857</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D347" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E347" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B348" t="n">
         <v>0</v>
       </c>
       <c r="C348" t="n">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D348" t="n">
-        <v>-0.6333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E348" t="b">
         <v>1</v>
@@ -6884,36 +6842,34 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B349" t="n">
-        <v>-3</v>
-      </c>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
       <c r="C349" t="n">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D349" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E349" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B350" t="n">
         <v>0</v>
       </c>
       <c r="C350" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D350" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.2</v>
       </c>
       <c r="E350" t="b">
         <v>1</v>
@@ -6922,17 +6878,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B351" t="n">
         <v>0</v>
       </c>
       <c r="C351" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D351" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E351" t="b">
         <v>1</v>
@@ -6941,17 +6897,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B352" t="n">
         <v>0</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D352" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E352" t="b">
         <v>1</v>
@@ -6960,17 +6916,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B353" t="n">
         <v>0</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D353" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E353" t="b">
         <v>1</v>
@@ -6979,17 +6935,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B354" t="n">
         <v>0</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D354" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E354" t="b">
         <v>1</v>
@@ -6998,26 +6954,24 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B355" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
-        <v>-0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="D355" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="E355" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -7027,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="D356" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E356" t="b">
         <v>1</v>
@@ -7036,7 +6990,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -7046,7 +7000,7 @@
         <v>0</v>
       </c>
       <c r="D357" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E357" t="b">
         <v>1</v>
@@ -7055,7 +7009,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -7065,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="D358" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E358" t="b">
         <v>1</v>
@@ -7074,7 +7028,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -7084,7 +7038,7 @@
         <v>0</v>
       </c>
       <c r="D359" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E359" t="b">
         <v>1</v>
@@ -7093,7 +7047,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -7103,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="D360" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E360" t="b">
         <v>1</v>
@@ -7112,7 +7066,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -7122,7 +7076,7 @@
         <v>0</v>
       </c>
       <c r="D361" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E361" t="b">
         <v>1</v>
@@ -7131,7 +7085,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -7141,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="D362" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E362" t="b">
         <v>1</v>
@@ -7150,7 +7104,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -7160,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="D363" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E363" t="b">
         <v>1</v>
@@ -7169,7 +7123,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -7179,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="D364" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E364" t="b">
         <v>1</v>
@@ -7188,7 +7142,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -7198,7 +7152,7 @@
         <v>0</v>
       </c>
       <c r="D365" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E365" t="b">
         <v>1</v>
@@ -7207,7 +7161,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -7217,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="D366" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E366" t="b">
         <v>1</v>
@@ -7226,7 +7180,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -7236,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="D367" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E367" t="b">
         <v>1</v>
@@ -7245,7 +7199,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -7255,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="D368" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="E368" t="b">
         <v>1</v>
@@ -7264,17 +7218,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="C369" t="n">
-        <v>0</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D369" t="n">
-        <v>-0.6333333333333333</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="E369" t="b">
         <v>1</v>
@@ -7283,34 +7237,32 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="B370" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
       <c r="C370" t="n">
-        <v>0</v>
+        <v>-0.8571428571428571</v>
       </c>
       <c r="D370" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="E370" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="n">
-        <v>0</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D371" t="n">
-        <v>-0.4333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="E371" t="b">
         <v>0</v>
@@ -7319,55 +7271,51 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="B372" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
       <c r="C372" t="n">
-        <v>0</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D372" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.4</v>
       </c>
       <c r="E372" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="B373" t="n">
-        <v>0</v>
-      </c>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
       <c r="C373" t="n">
-        <v>0</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D373" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E373" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B374" t="n">
         <v>0</v>
       </c>
       <c r="C374" t="n">
-        <v>0</v>
+        <v>-2.142857142857143</v>
       </c>
       <c r="D374" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="E374" t="b">
         <v>1</v>
@@ -7376,51 +7324,55 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr"/>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>-2</v>
+      </c>
       <c r="C375" t="n">
-        <v>0</v>
+        <v>-2.428571428571428</v>
       </c>
       <c r="D375" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E375" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr"/>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>-2</v>
+      </c>
       <c r="C376" t="n">
-        <v>0</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="D376" t="n">
-        <v>-0.1</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E376" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B377" t="n">
         <v>0</v>
       </c>
       <c r="C377" t="n">
-        <v>0</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D377" t="n">
-        <v>-0.1</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E377" t="b">
         <v>1</v>
@@ -7429,17 +7381,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B378" t="n">
         <v>0</v>
       </c>
       <c r="C378" t="n">
-        <v>0</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D378" t="n">
-        <v>-0.1</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E378" t="b">
         <v>1</v>
@@ -7448,34 +7400,36 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr"/>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>-3</v>
+      </c>
       <c r="C379" t="n">
-        <v>0</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="D379" t="n">
-        <v>0</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E379" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B380" t="n">
         <v>0</v>
       </c>
       <c r="C380" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D380" t="n">
-        <v>0</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E380" t="b">
         <v>1</v>
@@ -7484,17 +7438,17 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B381" t="n">
         <v>0</v>
       </c>
       <c r="C381" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D381" t="n">
-        <v>0</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E381" t="b">
         <v>1</v>
@@ -7503,17 +7457,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B382" t="n">
         <v>0</v>
       </c>
       <c r="C382" t="n">
-        <v>0</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D382" t="n">
-        <v>0</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E382" t="b">
         <v>1</v>
@@ -7522,17 +7476,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.2857142857142857</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D383" t="n">
-        <v>-0.06666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E383" t="b">
         <v>1</v>
@@ -7541,85 +7495,93 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr"/>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0</v>
+      </c>
       <c r="C384" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D384" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E384" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr"/>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>0</v>
+      </c>
       <c r="C385" t="n">
-        <v>-0.8571428571428571</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="D385" t="n">
-        <v>-0.2</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E385" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr"/>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>0</v>
+      </c>
       <c r="C386" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D386" t="n">
-        <v>-0.2666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E386" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr"/>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>0</v>
+      </c>
       <c r="C387" t="n">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D387" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E387" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C388" t="n">
-        <v>-1.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D388" t="n">
-        <v>-0.4</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E388" t="b">
         <v>1</v>
@@ -7628,17 +7590,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C389" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D389" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E389" t="b">
         <v>1</v>
@@ -7647,17 +7609,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B390" t="n">
         <v>0</v>
       </c>
       <c r="C390" t="n">
-        <v>-1.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D390" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E390" t="b">
         <v>1</v>
@@ -7666,17 +7628,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B391" t="n">
         <v>0</v>
       </c>
       <c r="C391" t="n">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D391" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E391" t="b">
         <v>1</v>
@@ -7685,17 +7647,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="B392" t="n">
         <v>0</v>
       </c>
       <c r="C392" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D392" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E392" t="b">
         <v>1</v>
@@ -7704,17 +7666,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B393" t="n">
         <v>0</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D393" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E393" t="b">
         <v>1</v>
@@ -7723,34 +7685,36 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr"/>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>0</v>
+      </c>
       <c r="C394" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D394" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B395" t="n">
         <v>0</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D395" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E395" t="b">
         <v>1</v>
@@ -7759,17 +7723,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D396" t="n">
-        <v>-0.5333333333333333</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E396" t="b">
         <v>1</v>
@@ -7778,86 +7742,644 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr"/>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>0</v>
+      </c>
       <c r="C397" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="D397" t="n">
-        <v>-0.6</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E397" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr"/>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>0</v>
+      </c>
       <c r="C398" t="n">
-        <v>-0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D398" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E398" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr"/>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>0</v>
+      </c>
       <c r="C399" t="n">
-        <v>-1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="D399" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="E399" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr"/>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0</v>
+      </c>
       <c r="C400" t="n">
-        <v>-1.428571428571429</v>
+        <v>0</v>
       </c>
       <c r="D400" t="n">
-        <v>-0.8</v>
+        <v>-0.5333333333333333</v>
       </c>
       <c r="E400" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
       <c r="C401" t="n">
+        <v>0</v>
+      </c>
+      <c r="D401" t="n">
+        <v>-0.4333333333333333</v>
+      </c>
+      <c r="E401" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>0</v>
+      </c>
+      <c r="C402" t="n">
+        <v>0</v>
+      </c>
+      <c r="D402" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E402" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>0</v>
+      </c>
+      <c r="C403" t="n">
+        <v>0</v>
+      </c>
+      <c r="D403" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E403" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>0</v>
+      </c>
+      <c r="C404" t="n">
+        <v>0</v>
+      </c>
+      <c r="D404" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="E404" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="n">
+        <v>0</v>
+      </c>
+      <c r="D405" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="E405" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="n">
+        <v>0</v>
+      </c>
+      <c r="D406" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E406" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>0</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0</v>
+      </c>
+      <c r="D407" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E407" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>0</v>
+      </c>
+      <c r="C408" t="n">
+        <v>0</v>
+      </c>
+      <c r="D408" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E408" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="n">
+        <v>0</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>0</v>
+      </c>
+      <c r="C410" t="n">
+        <v>0</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>0</v>
+      </c>
+      <c r="C411" t="n">
+        <v>0</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>0</v>
+      </c>
+      <c r="C412" t="n">
+        <v>0</v>
+      </c>
+      <c r="D412" t="n">
+        <v>0</v>
+      </c>
+      <c r="E412" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C413" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D413" t="n">
+        <v>-0.06666666666666667</v>
+      </c>
+      <c r="E413" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D414" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="E414" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D415" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E415" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D416" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="E416" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D417" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E417" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C418" t="n">
         <v>-1.714285714285714</v>
       </c>
-      <c r="D401" t="n">
-        <v>-0.8666666666666667</v>
-      </c>
-      <c r="E401" t="b">
-        <v>0</v>
+      <c r="D418" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E418" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C419" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D419" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E419" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>0</v>
+      </c>
+      <c r="C420" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="D420" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E420" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>0</v>
+      </c>
+      <c r="C421" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="D421" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E421" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>0</v>
+      </c>
+      <c r="C422" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D422" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E422" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>0</v>
+      </c>
+      <c r="C423" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D423" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E423" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D424" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E424" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>0</v>
+      </c>
+      <c r="C425" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D425" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E425" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C426" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D426" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E426" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D427" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E427" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D428" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E428" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>0</v>
+      </c>
+      <c r="C429" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D429" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E429" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>0</v>
+      </c>
+      <c r="C430" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D430" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E430" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>0</v>
+      </c>
+      <c r="C431" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D431" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E431" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7890,7 +8412,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-02-19 to 2026-03-25 | Publication days: 335</t>
+          <t>Coverage: 2025-01-20 to 2026-03-25 | Publication days: 341</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -8403,21 +8415,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>India WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2025-01-20 to 2026-03-25 | Publication days: 341</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -8425,22 +8437,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E431"/>
+  <dimension ref="A1:E432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -8392,6 +8380,23 @@
       </c>
       <c r="E431" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="n">
+        <v>-0.8571428571428571</v>
+      </c>
+      <c r="D432" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E432" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8415,21 +8420,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>India WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2025-01-20 to 2026-03-25 | Publication days: 341</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2025-01-20 to 2026-03-26 | Publication days: 341</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -8437,22 +8442,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -8420,21 +8432,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>India WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2025-01-20 to 2026-03-26 | Publication days: 341</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -8442,22 +8454,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -8400,7 +8388,9 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr"/>
+      <c r="B432" t="n">
+        <v>0</v>
+      </c>
       <c r="C432" t="n">
         <v>-0.8571428571428571</v>
       </c>
@@ -8408,7 +8398,7 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E432" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8432,21 +8422,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>India WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2025-01-20 to 2026-03-26 | Publication days: 341</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2025-01-20 to 2026-03-26 | Publication days: 342</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -8454,22 +8444,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -8422,21 +8434,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>India WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2025-01-20 to 2026-03-26 | Publication days: 342</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -8444,22 +8456,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E432"/>
+  <dimension ref="A1:E433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -8411,6 +8399,23 @@
       </c>
       <c r="E432" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D433" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E433" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8434,21 +8439,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>India WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2025-01-20 to 2026-03-26 | Publication days: 342</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2025-01-20 to 2026-03-27 | Publication days: 342</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -8456,22 +8461,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -8407,7 +8407,9 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr"/>
+      <c r="B433" t="n">
+        <v>0</v>
+      </c>
       <c r="C433" t="n">
         <v>-0.5714285714285714</v>
       </c>
@@ -8415,7 +8417,7 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E433" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8448,7 +8450,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-03-27 | Publication days: 342</t>
+          <t>Coverage: 2025-01-20 to 2026-03-27 | Publication days: 343</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E433"/>
+  <dimension ref="A1:E434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8418,6 +8418,23 @@
       </c>
       <c r="E433" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D434" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E434" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8450,7 +8467,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-03-27 | Publication days: 343</t>
+          <t>Coverage: 2025-01-20 to 2026-03-28 | Publication days: 343</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8435,6 +8435,25 @@
       </c>
       <c r="E434" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>0</v>
+      </c>
+      <c r="C435" t="n">
+        <v>0</v>
+      </c>
+      <c r="D435" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E435" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8467,7 +8486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-03-28 | Publication days: 343</t>
+          <t>Coverage: 2025-01-20 to 2026-03-29 | Publication days: 344</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E435"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8454,6 +8454,23 @@
       </c>
       <c r="E435" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="n">
+        <v>0</v>
+      </c>
+      <c r="D436" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E436" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8486,7 +8503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-03-29 | Publication days: 344</t>
+          <t>Coverage: 2025-01-20 to 2026-03-30 | Publication days: 344</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E436"/>
+  <dimension ref="A1:E437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8471,6 +8471,25 @@
       </c>
       <c r="E436" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>0</v>
+      </c>
+      <c r="C437" t="n">
+        <v>0</v>
+      </c>
+      <c r="D437" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E437" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8503,7 +8522,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-03-30 | Publication days: 344</t>
+          <t>Coverage: 2025-01-20 to 2026-03-31 | Publication days: 345</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E437"/>
+  <dimension ref="A1:E438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8489,6 +8489,25 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E437" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>0</v>
+      </c>
+      <c r="C438" t="n">
+        <v>0</v>
+      </c>
+      <c r="D438" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E438" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8522,7 +8541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-03-31 | Publication days: 345</t>
+          <t>Coverage: 2025-01-20 to 2026-04-01 | Publication days: 346</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E438"/>
+  <dimension ref="A1:E439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8508,6 +8508,25 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E438" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>0</v>
+      </c>
+      <c r="C439" t="n">
+        <v>0</v>
+      </c>
+      <c r="D439" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E439" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8541,7 +8560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-01 | Publication days: 346</t>
+          <t>Coverage: 2025-01-20 to 2026-04-02 | Publication days: 347</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E439"/>
+  <dimension ref="A1:E440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8527,6 +8527,25 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E439" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>0</v>
+      </c>
+      <c r="C440" t="n">
+        <v>0</v>
+      </c>
+      <c r="D440" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E440" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8560,7 +8579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-02 | Publication days: 347</t>
+          <t>Coverage: 2025-01-20 to 2026-04-03 | Publication days: 348</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E440"/>
+  <dimension ref="A1:E441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8547,6 +8547,23 @@
       </c>
       <c r="E440" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="n">
+        <v>0</v>
+      </c>
+      <c r="D441" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E441" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8579,7 +8596,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-03 | Publication days: 348</t>
+          <t>Coverage: 2025-01-20 to 2026-04-04 | Publication days: 348</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E441"/>
+  <dimension ref="A1:E442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8563,6 +8563,23 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E441" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="n">
+        <v>0</v>
+      </c>
+      <c r="D442" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E442" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8596,7 +8613,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-04 | Publication days: 348</t>
+          <t>Coverage: 2025-01-20 to 2026-04-05 | Publication days: 348</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E442"/>
+  <dimension ref="A1:E443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8580,6 +8580,23 @@
         <v>-0.6666666666666666</v>
       </c>
       <c r="E442" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="n">
+        <v>0</v>
+      </c>
+      <c r="D443" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E443" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8613,7 +8630,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-05 | Publication days: 348</t>
+          <t>Coverage: 2025-01-20 to 2026-04-06 | Publication days: 348</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E443"/>
+  <dimension ref="A1:E444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8518,13 +8518,13 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C439" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D439" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E439" t="b">
         <v>1</v>
@@ -8540,10 +8540,10 @@
         <v>0</v>
       </c>
       <c r="C440" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D440" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E440" t="b">
         <v>1</v>
@@ -8557,10 +8557,10 @@
       </c>
       <c r="B441" t="inlineStr"/>
       <c r="C441" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D441" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E441" t="b">
         <v>0</v>
@@ -8574,10 +8574,10 @@
       </c>
       <c r="B442" t="inlineStr"/>
       <c r="C442" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D442" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E442" t="b">
         <v>0</v>
@@ -8589,15 +8589,36 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr"/>
+      <c r="B443" t="n">
+        <v>0</v>
+      </c>
       <c r="C443" t="n">
-        <v>0</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D443" t="n">
-        <v>-0.6</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E443" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C444" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="D444" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="E444" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8630,7 +8651,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-06 | Publication days: 348</t>
+          <t>Coverage: 2025-01-20 to 2026-04-07 | Publication days: 350</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E444"/>
+  <dimension ref="A1:E445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8518,13 +8518,13 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D439" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E439" t="b">
         <v>1</v>
@@ -8540,10 +8540,10 @@
         <v>0</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D440" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E440" t="b">
         <v>1</v>
@@ -8557,10 +8557,10 @@
       </c>
       <c r="B441" t="inlineStr"/>
       <c r="C441" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D441" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E441" t="b">
         <v>0</v>
@@ -8574,10 +8574,10 @@
       </c>
       <c r="B442" t="inlineStr"/>
       <c r="C442" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D442" t="n">
-        <v>-0.7333333333333333</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="E442" t="b">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="D443" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6</v>
       </c>
       <c r="E443" t="b">
         <v>1</v>
@@ -8612,12 +8612,31 @@
         <v>-2</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.2857142857142857</v>
       </c>
       <c r="D444" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.6</v>
       </c>
       <c r="E444" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0</v>
+      </c>
+      <c r="C445" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D445" t="n">
+        <v>-0.5333333333333333</v>
+      </c>
+      <c r="E445" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8651,7 +8670,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-07 | Publication days: 350</t>
+          <t>Coverage: 2025-01-20 to 2026-04-08 | Publication days: 351</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E445"/>
+  <dimension ref="A1:E446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8637,6 +8637,25 @@
         <v>-0.5333333333333333</v>
       </c>
       <c r="E445" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>0</v>
+      </c>
+      <c r="C446" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D446" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E446" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8670,7 +8689,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-08 | Publication days: 351</t>
+          <t>Coverage: 2025-01-20 to 2026-04-09 | Publication days: 352</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E446"/>
+  <dimension ref="A1:E447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8656,6 +8656,25 @@
         <v>-0.4666666666666667</v>
       </c>
       <c r="E446" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>0</v>
+      </c>
+      <c r="C447" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D447" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E447" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8689,7 +8708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-09 | Publication days: 352</t>
+          <t>Coverage: 2025-01-20 to 2026-04-10 | Publication days: 353</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E447"/>
+  <dimension ref="A1:E448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8675,6 +8675,25 @@
         <v>-0.4</v>
       </c>
       <c r="E447" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>0</v>
+      </c>
+      <c r="C448" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D448" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="E448" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8708,7 +8727,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-10 | Publication days: 353</t>
+          <t>Coverage: 2025-01-20 to 2026-04-11 | Publication days: 354</t>
         </is>
       </c>
     </row>

--- a/data/IN.xlsx
+++ b/data/IN.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E448"/>
+  <dimension ref="A1:E449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8695,6 +8695,23 @@
       </c>
       <c r="E448" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="D449" t="n">
+        <v>-0.2666666666666667</v>
+      </c>
+      <c r="E449" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8727,7 +8744,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2025-01-20 to 2026-04-11 | Publication days: 354</t>
+          <t>Coverage: 2025-01-20 to 2026-04-12 | Publication days: 354</t>
         </is>
       </c>
     </row>
